--- a/data/Evaluasi_Anotasi.xlsx
+++ b/data/Evaluasi_Anotasi.xlsx
@@ -479,32 +479,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>c#
-collaborative
-communication
-communication skill
-development tools
-enterprise resource planning
-erp
-erp based applications
-git
-information engineering
-information system
-information systems
-java
-manage databases
-mysql
-object orient programming
-object oriented programming
-oop
-php
-postgresql
-programming language
-sql
-sql database
-sql server
-visual studio
-write</t>
+          <t>c#, collaborative, communication, communication skill, development tools, enterprise resource planning, erp, erp based applications, git, information engineering, information system, information systems, java, manage databases, mysql, object orient programming, object oriented programming, oop, php, postgresql, programming language, sql, sql database, sql server, visual studio, write</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -534,48 +509,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>analytical
-analytical skills
-analyze test
-appium
-application testing
-automated testing
-bug reports
-bugs system
-business requirements
-collaborate
-compile
-computer science
-critical thinking
-design
-design principles
-develop
-english
-english proficiency
-identify bugs
-implement
-indonesian
-information technology
-information tehnology
-manual testing
-ownership
-postman
-proactive
-problem solving
-qa tools
-quality assurance
-regression testing
-responsible
-scripts
-selenium
-software testing
-system fixes
-test
-test scenarios
-ui/ux design
-usability testing
-user feedback
-user interface</t>
+          <t>analytical skills, appium, application testing, automated testing, bug reports, bugs system, business requirement, collaborate, compile, computer science, critical thinking, design principles, english, identify bugs, implement, information technology, information tehnology, manual testing, postman, problem solving, quality assurance, regression testing, responsible, scripts, selenium, software testing, system fixes, test, test scenarios, ui/ux design, usability testing, user feedback, user interface</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -585,16 +519,16 @@
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
         <v>0.6875</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5945945945945946</v>
+        <v>0.676923076923077</v>
       </c>
     </row>
     <row r="4">
@@ -605,38 +539,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>.net
-accountability
-angularjs
-api
-application lifecycle management
-asp.net
-asp.net mvc
-c#
-computer science
-css
-engineering
-git
-html
-information technology
-javascript
-jquery
-mcsd
-mvc
-object oriented programming
-ownership
-razor
-rest
-self motivated
-soap
-sql
-supervision
-t sql
-telerik
-vsts
-wcf
-web api
-web services</t>
+          <t>.net, accountability, angularjs, api, application lifecycle management, asp.net, asp.net mvc, c#, computer science, css, engineering, git, html, information technology, javascript, jquery, mcsd, mvc, object oriented programming, ownership, razor, rest, self motivated, soap, sql, supervision, t sql, telerik, vsts, wcf, web api, web services</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -666,49 +569,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>adapt
-ai
-ai technologies
-analyze
-bug fixing
-computer science
-curiosity
-fix
-fix programming bugs
-libraries
-programming languages
-relational database
-scalable
-scalable code
-software applications
-software design
-software development
-software maintenance
-sql
-sql database
-testable
-testable code
-web application
-web applications</t>
+          <t>adapt, ai, ai technologies, analyze, computer science, curiosity, fix, fix programming bugs, programming languages, relational database, scalable, software applications, software development, sql, sql database, testable code, web applications</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="H5" t="n">
-        <v>0.631578947368421</v>
+        <v>0.5161290322580646</v>
       </c>
     </row>
     <row r="6">
@@ -719,37 +599,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>accounting
-ad hoc
-ad hoc reports
-analysis
-analysis workflow
-analytical enhancements
-analyze
-analyze data
-business
-business needs
-collaboratively
-communication
-communication skills
-cross functional teams
-data
-data analysis
-data processing
-english
-excel macro
-excel macros
-industrial engineering
-information systems
-initiatives
-management
-management needs
-microsoft excel
-prioritize
-reporting
-support
-task prioritization
-vba</t>
+          <t>accounting, ad hoc, ad hoc reports, analysis, analysis workflow, analytical enhancements, analyze, analyze data, business, business needs, collaboratively, communication, communication skills, cross functional teams, data, data analysis, data processing, english, excel macro, excel macros, industrial engineering, information systems, initiatives, management, management needs, microsoft excel, prioritize, reporting, support, task prioritization, vba</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -779,34 +629,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>analytical
-apis
-backend
-backend developer
-best practices
-coding
-collaborating
-computer science
-cross functional teams
-databases
-design
-high performance
-indepedently
-informatics engineering
-information system
-maintain
-mobile app
-mobile app development
-scalable
-secure
-secure applications
-security
-security best practices
-server side
-server side applications
-system architecture
-time management
-web app</t>
+          <t>analytical, apis, backend, backend developer, best practices, coding, collaborating, computer science, cross functional teams, databases, design, high performance, informatics engineering, information system, maintain, mobile app, mobile app development, scalable, secure, secure applications, security, security best practices, server side, system architecture, time management, web app</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -816,16 +639,16 @@
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F7" t="n">
         <v>0.7777777777777778</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.6363636363636364</v>
       </c>
     </row>
     <row r="8">
@@ -836,34 +659,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>api
-based system
-communicate
-crawler
-data acquisition
-data operations
-data quality
-data requirements
-elasticsearch
-javascript
-kafka
-large scale systems
-linux
-mariadb
-node
-postgres
-programming languages
-python
-redis
-robust
-scala
-scale
-social media
-social media crawler
-spark
-sql
-web scraping
-webscraping</t>
+          <t>api, based system, communicate, crawler, data acquisition, data operations, data quality, data requirements, elasticsearch, javascript, kafka, large scale systems, linux, mariadb, node, postgres, programming languages, python, redis, robust, scala, scale, social media, social media crawler, spark, sql, web scraping, webscraping</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -893,60 +689,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>analytical
-analytical skill
-analyze
-audit reports
-auditing
-audits
-collaborate
-communication
-computer science
-cybersecurity
-cybesecurity
-governance risk
-information security
-information system
-information systems
-information technology
-interpersonal
-interpersonal skills
-it auditing
-it compliance
-it controls
-it governance
-it systems
-network security
-penetration testing
-proactive
-problem solve
-problem solving
-programming
-risk assessment
-risk management
-software programming
-system control
-system software
-vulnerabilities</t>
+          <t>analytical skill, analyze, audit reports, auditing, audits, collaborate, communication, computer science, cybersecurity, cybesecurity, governance risk, information security, information system, information technology, interpersonal, it compliance, it controls, it governance, network security, penetration testing, proactive, problem solve, problem solving, programming, risk assessment, risk management, system control, vulnerabilities</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.7547169811320756</v>
       </c>
     </row>
     <row r="10">
@@ -957,42 +719,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ai
-business use cases
-clean code
-computer science
-data engineers
-data preprocessing
-deep learning
-deploy
-design
-develop
-docker
-git
-machine learning
-maintainable code
-ml
-ml pipelines
-mlops
-model deployment
-model monitoring
-model optimization
-model validation
-monitor
-optimize
-pipelines
-preprocess
-problem solving
-production systems
-python
-pytorch
-research
-scikit learn
-software
-software developers
-software development
-teamwork
-tensorflow</t>
+          <t>ai, business use cases, clean code, computer science, data engineers, data preprocessing, deep learning, deploy, design, develop, docker, git, machine learning, maintainable code, ml, ml pipelines, mlops, model deployment, model monitoring, model optimization, model validation, monitor, optimize, pipelines, preprocess, problem solving, production systems, python, pytorch, research, scikit learn, software, software developers, software development, teamwork, tensorflow</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1022,31 +749,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>agile
-analytical
-collaboration
-communication
-communication skills
-computer science
-effective collaboration
-engineering
-git
-kafka
-message broker
-message brokers
-ms sql server
-mysql
-postgresql
-problem solve
-problem solving
-rabbitmq
-rdbms
-scrum
-sql server
-strong troubleshooting
-troubleshooting
-version control
-version control system</t>
+          <t>agile, analytical, collaboration, communication, communication skills, computer science, effective collaboration, engineering, git, kafka, message broker, message brokers, ms sql server, mysql, postgresql, problem solve, problem solving, rabbitmq, rdbms, scrum, sql server, strong troubleshooting, troubleshooting, version control, version control system</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1076,48 +779,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>automation
-best practices
-cache
-cache handling
-clean code
-collaborative
-computer science
-computer science fundamentals
-continuous integration
-data structures
-database logic
-design patterns
-django
-fastapi
-feature development
-git
-http protocol
-key value database
-libraries
-linux
-linux development environment
-maintainable code
-memcached
-nosql
-performance optimization
-programming
-python
-redis
-reusable code
-scalability
-software development
-software engineering best practices
-source control
-sql
-unit testing
-user experience
-web backend services
-web development
-web service framework
-web service frameworks
-web technologies
-working experience</t>
+          <t>automation, best practices, cache, cache handling, clean code, collaborative, computer science, computer science fundamentals, continuous integration, data structures, database logic, design patterns, django, fastapi, feature development, git, http protocol, key value database, libraries, linux, linux development environment, maintainable code, memcached, nosql, performance optimization, programming, python, redis, reusable code, scalability, software development, software engineering best practices, source control, sql, unit testing, user experience, web backend services, web development, web service framework, web service frameworks, web technologies, working experience</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1147,44 +809,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>automate
-backup solution
-cli
-cyber security
-data security
-enterprise backup solution
-firewall
-firewalls
-flexible
-ha
-hardwares
-informatics engineering
-information technology
-infrastructure
-ip segmentation
-ip segments
-it infrastructure
-it operations
-it sysadmin
-it systems
-l1
-l2 support
-mikrotik
-network
-network operation system
-operating system
-operations
-programming
-scripting
-security device
-server
-server operation system
-software engineering
-sql
-switches
-troubleshooting
-vm
-vps</t>
+          <t>automate, backup solution, cli, cyber security, data security, firewalls, flexible, hardwares, informatics engineering, information technology, infrastructure, ip segments, it infrastructure, mikrotik, network, operating system, operations, programming, scripting, security device, server, software engineering, sql, switches, troubleshooting, vm, vps</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1194,16 +819,16 @@
         <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
         <v>0.7083333333333334</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4473684210526316</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5483870967741936</v>
+        <v>0.6666666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -1214,69 +839,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>agile
-analysis
-attention to detail
-automate
-bi engineer
-bi tools
-collaborate
-communication
-communication skills
-computer science
-dashboards
-data analysis
-data analyst
-data architecture
-data governance
-data modeling
-data modelling
-data pipelines
-data warehousing
-data warehousing concepts
-datasets
-design
-develop
-development environment
-etl
-information systems
-looker
-maintain
-optimize
-power bi
-problem solving
-relational database
-root cause analysis
-scheduling skill
-sql
-statistics
-superset
-support business
-tableau
-tableu
-transform data
-troubleshooting skill
-visualizations
-workflows</t>
+          <t>agile, analysis, attention to detail, automate, bi engineer, bi tools, collaborate, communication skills, computer science, dashboards, data analyst, data architecture, data governance, data modeling, data modelling, data pipelines, data warehousing, data warehousing concepts, datasets, design, develop, development environment, etl, information systems, looker, maintain, optimize, power bi, problem solving, relational database, root cause analysis, scheduling skill, sql, statistics, superset, support business, tableau, tableu, transform data, troubleshooting skill, visualizations, workflows</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="G14" t="n">
         <v>0.5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5866666666666667</v>
+        <v>0.5753424657534247</v>
       </c>
     </row>
     <row r="15">
@@ -1287,38 +869,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>agile scrum
-agile scrum framework
-analyze
-api
-app maintenance
-application
-application support
-apps development
-banking
-bug troubleshooting
-code testing
-collaboration
-communication
-database
-design
-java
-loan
-manage documentation
-microservice
-monitor
-mysql
-operational
-postgresql
-scrum
-software security
-system integration
-system integration test
-system monitor
-system testing
-technological developments
-troubleshooting
-unit tests</t>
+          <t>agile scrum, agile scrum framework, analyze, api, app maintenance, application, application support, apps development, banking, bug troubleshooting, code testing, collaboration, communication, database, design, java, loan, manage documentation, microservice, monitor, mysql, operational, postgresql, scrum, software security, system integration, system integration test, system monitor, system testing, technological developments, troubleshooting, unit tests</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1348,22 +899,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>analytical
-bug tracking
-computer science
-indepedently
-information technology
-organizational
-organizational skill
-problem solve
-problem solving
-qa testing
-software development
-software testing
-test automation
-test case
-testing
-testing methodologies</t>
+          <t>analytical, bug tracking, computer science, indepedently, information technology, organizational, organizational skill, problem solve, problem solving, qa testing, software development, software testing, test automation, test case, testing, testing methodologies</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1393,24 +929,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>basic technical terms
-business it
-business it support
-cloud technology
-coordination
-desktop support
-english
-hardware
-hardware support
-installation
-it security
-it technologies
-network
-network support
-project support
-software support
-troubleshooting
-write english</t>
+          <t>basic technical terms, business it, business it support, cloud technology, coordination, desktop support, english, hardware, hardware support, installation, it security, it technologies, network, network support, project support, software support, troubleshooting, write english</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1440,54 +959,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>adapting
-adaptive
-adobe illustrator
-analyze
-canva
-collaborated
-concistency
-creating design system
-design decision
-design guidelines
-design specification
-design system
-documenting design
-figma
-interactive prototype
-plan
-presentation design
-prototype
-responsibility
-testing
-typography
-ui/ux
-usability test
-usability testing
-user research
-ux
-wireframes
-work together
-workflows</t>
+          <t>adapting, adobe illustrator, analyze, canva, collaborated, concistency, creating design system, design decision, design decisions, design specification, design specifications, design system, documenting design, figma, interactive prototype, plan, presentation design, responsibility, testing, typography, ui/ux, usability testing, user research, wireframes, work together, workflows</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F18" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5172413793103449</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6122448979591838</v>
+        <v>0.608695652173913</v>
       </c>
     </row>
     <row r="19">
@@ -1498,19 +989,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>communication information technology
-css
-customer relationship menagement
-design ideas
-design tools
-graphic desi
-graphic design tool
-html
-information engineering
-javascript
-user experience
-web design
-wordpress</t>
+          <t>communication information technology, css, customer relationship menagement, design ideas, design tools, graphic desi, graphic design tool, html, information engineering, javascript, user experience, web design, wordpress</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1540,33 +1019,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>angular
-back end
-backend
-basic troubleshooting
-code review
-code reviews
-collaborative
-computer science
-css
-fast paced
-flutter
-front end
-frontend
-full stack development
-fullstack development
-html
-information technology
-java
-javascript
-managing multiple task
-mobile
-modern javascript framework
-rest api
-spring boot
-spring boot framework
-team leader
-troubleshooting</t>
+          <t>angular, back end, backend, basic troubleshooting, code review, code reviews, collaborative, computer science, css, fast paced, flutter, front end, frontend, full stack development, fullstack development, html, information technology, java, javascript, managing multiple task, mobile, modern javascript framework, rest api, spring boot, spring boot framework, team leader, troubleshooting</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1596,45 +1049,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1st level support
-computer
-computer engineering
-computer science
-customer support
-electrical engineering
-information technology
-it operation
-it operation monitoring
-meraki
-monitoring
-network routing
-network troubleshooting
-security monitoring
-switch
-switching
-switching cisco
-technical support
-technical support engineer
-troubleshooting</t>
+          <t>computer engineering, computer science, electrical engineering, information technology, it operation monitoring, meraki, network routing, network troubleshooting, security monitoring, switching, switching cisco, technical support engineer</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H21" t="n">
-        <v>0.625</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
   </sheetData>
@@ -1701,16 +1135,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>design code
-documentation
-programming
-refactor
-refactors
-scripts
-software development
-software services
-test
-tests</t>
+          <t>design code, documentation, programming, refactor, refactors, scripts, software development, software services, test, tests</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1740,14 +1165,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>adoption
-create value
-data science
-decision make
-innovation
-insights
-organisational policy
-plans</t>
+          <t>adoption, create value, data science, decision make, innovation, insights, organisational policy, plans</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1777,20 +1195,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>algorithms
-business requirement
-collaborates
-cross functional teams
-deployment
-development
-engineers features
-evaluation
-integrate learning
-machine learning
-monitoring
-performance analysis
-production system
-troubleshoot</t>
+          <t>algorithms, business requirement, collaborates, cross functional teams, deployment, development, engineers features, evaluation, integrate learning, machine learning, monitoring, performance analysis, production system, troubleshoot</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1820,18 +1225,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>adoption
-aligns business
-analytics
-business strategy
-cross functional
-data analytics
-data science
-governance
-leadership
-organisational performance
-strategic application
-transformation</t>
+          <t>adoption, aligns business, analytics, business strategy, cross functional, data analytics, data science, governance, leadership, organisational performance, strategic application, transformation</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1861,21 +1255,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>applications
-continuous integration
-data conversion
-data engineering
-data governance
-data migration
-data pipeline
-data quality
-data stores
-deployment
-pipeline performance
-quality checking
-remediation
-scalability
-security standards</t>
+          <t>applications, continuous integration, data conversion, data engineering, data governance, data migration, data pipeline, data quality, data stores, deployment, pipeline performance, quality checking, remediation, scalability, security standards</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1905,17 +1285,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>advises
-collaborates
-communicate
-data visualisation
-decision
-decision make
-develop plans
-identify
-parameters
-requirements plans
-target audience</t>
+          <t>advises, collaborates, communicate, data visualisation, decision, decision make, develop plans, identify, parameters, requirements plans, target audience</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1945,23 +1315,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>brand
-design assessement
-design assignments
-design concepts
-design processes
-design quality
-designs concepts
-designs visual
-document design
-document requirements
-effectiveness
-evidence base practice
-good practices
-interactive
-interactive prototypes
-manages design
-mock up</t>
+          <t>brand, design assessement, design assignments, design concepts, design processes, design quality, designs concepts, designs visual, document design, document requirements, effectiveness, evidence base practice, good practices, interactive, interactive prototypes, manages design, mock up</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1991,17 +1345,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>analyses
-incident communication
-incident management
-incident resolution
-management process
-manages incident
-operation
-regulatory requiremenet
-regulatory requirement
-reports
-targets</t>
+          <t>analyses, incident communication, incident management, incident resolution, management process, manages incident, operation, regulatory requiremenet, regulatory requirement, reports, targets</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2031,14 +1375,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>coordinates
-mitigate control
-penetration testing
-plans
-responsiblity
-security testing
-testing activities
-vulnerabilities</t>
+          <t>coordinates, mitigate control, penetration testing, plans, responsiblity, security testing, testing activities, vulnerabilities</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2068,22 +1405,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>budgets
-business priority
-change control
-communicates
-control process
-governance
-leadership
-manage change
-monitors performance
-performance metric
-product quality
-project management
-project quality
-risks
-schedule
-timelines</t>
+          <t>budgets, business priority, change control, communicates, control process, governance, leadership, manage change, monitors performance, performance metric, product quality, project management, project quality, risks, schedule, timelines</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2113,17 +1435,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>assessments
-corrective actions
-cross functional
-mechanisms
-organisational control
-plans
-quality assurance
-review
-reviews
-supply chain
-support activity</t>
+          <t>assessments, corrective actions, cross functional, mechanisms, organisational control, plans, quality assurance, review, reviews, supply chain, support activity</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2153,18 +1465,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>business risk
-compliance
-decision making
-governance
-integrating
-leadership
-management process
-mitigation
-organisational policy
-risk management
-support decision
-tools and techniques</t>
+          <t>business risk, compliance, decision making, governance, integrating, leadership, management process, mitigation, organisational policy, risk management, support decision, tools and techniques</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2194,19 +1495,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>architecture design
-architectures
-architectures standards
-construction
-design specification
-design specifications
-design view
-designs system
-functional requirement
-modelling techniques
-prototypes
-simulates
-system</t>
+          <t>architecture design, architectures, architectures standards, construction, design specification, design specifications, design view, designs system, functional requirement, modelling techniques, prototypes, simulates, system</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2236,21 +1525,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>adapts software
-analysis
-architects
-corrective action
-decision make
-design method
-develop software
-impact analysis
-prototypes
-simulations
-software applications
-software design
-software design techniques
-software design tools
-system management</t>
+          <t>adapts software, analysis, architects, corrective action, decision make, design method, develop software, impact analysis, prototypes, simulations, software applications, software design, software design techniques, software design tools, system management</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2280,20 +1555,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>access security
-architectures design
-audit controlos
-design
-functional reuqirement
-network
-network architecture
-network components
-network designs
-network topology
-operational
-parameters
-physical design
-validation</t>
+          <t>access security, architectures design, audit controlos, design, functional reuqirement, network, network architecture, network components, network designs, network topology, operational, parameters, physical design, validation</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2323,20 +1585,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>adoption
-architectural principles
-architecturl principle
-business strategy
-collaboration
-communicates corporate
-information control
-information control requirements
-information security
-monitors environmental
-organisational strategies
-security control
-security policy
-subject matter</t>
+          <t>adoption, architectural principles, architecturl principle, business strategy, collaboration, communicates corporate, information control, information control requirements, information security, monitors environmental, organisational strategies, security control, security policy, subject matter</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2366,18 +1615,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>address ethical concern
-audit
-communicate
-data ethics
-design
-design decisions
-engages stakeholders
-ethical considerations
-ethical reviews
-execute
-impact assessment
-leads</t>
+          <t>address ethical concern, audit, communicate, data ethics, design, design decisions, engages stakeholders, ethical considerations, ethical reviews, execute, impact assessment, leads</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2407,18 +1645,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>audit
-audit advice
-audits
-collaborates
-control mechanisms
-cross functional
-integrate
-investigation
-management
-organisational policy
-plans
-supply chain</t>
+          <t>audit, audit advice, audits, collaborates, control mechanisms, cross functional, integrate, investigation, management, organisational policy, plans, supply chain</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2448,14 +1675,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>adoption
-configuration design
-deployment
-deployment project
-organisational policy
-plans
-refactoring
-software configuration</t>
+          <t>adoption, configuration design, deployment, deployment project, organisational policy, plans, refactoring, software configuration</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2485,17 +1705,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>analytics
-business intelligence
-data systems
-data warehouse
-data warehouse architecture
-database design
-database management system
-design characteristics
-managemenet
-management system
-transactional data</t>
+          <t>analytics, business intelligence, data systems, data warehouse, data warehouse architecture, database design, database management system, design characteristics, managemenet, management system, transactional data</t>
         </is>
       </c>
       <c r="C21" t="n">
